--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  02.06.2025 a 08.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  02.06.2025 a 08.06.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B80EBA4A-41B3-46C5-AD12-C1E74672373A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79D594F8-BAB4-4043-88D5-CEA8CF90C0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="02.06" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="61">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Allianz</t>
-  </si>
-  <si>
-    <t>27/5/2025</t>
   </si>
   <si>
     <t>LIMBO</t>
@@ -175,6 +172,63 @@
   <si>
     <t xml:space="preserve">TATIANE SANTOS OLIVEIRA MAGALHAES            </t>
   </si>
+  <si>
+    <t>ANTONIO ROQUE VELOSO FREITAS CPF 33794260678</t>
+  </si>
+  <si>
+    <t>Sem retorno do segurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSEMARY MARINI                              </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: Foto 45º - Frente e Lateral Direita (Não tirou foto do passo solicitado.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE LEONARDO DOS SANTOS CARVALHO            </t>
+  </si>
+  <si>
+    <t>SOUZA CARREGAMENTO MECANIZADO E TRANSPORTADOR</t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: Documento do veículo (Não tirou foto do passo solicitado.). Foto 45º - Traseira e Lateral Direita (Não tirou foto do passo solicitado.). Hodômetro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA BAPTISTA LOPES DE CAMPOS              </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 02/06/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SABRINA BACCIN BARRETO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RITA DE CASSIA XAVIER                        </t>
+  </si>
+  <si>
+    <t>Bônus;</t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade efetuar a transferência de bônus para o(a) senhor(a) R
+ITA DE CASSIA XAVIER, pois este não consta no quadro de sócios da
+empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOSCANO RESTAURANTES DE PARATY LTDA EPP      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRACI LAURINDO                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTAURANTE E BAR MANGUACA LTDA ME           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIEL CARLOS LEMPO                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEUZA DA SILVA SANTOS                        </t>
+  </si>
 </sst>
 </file>
 
@@ -232,7 +286,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -370,12 +424,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -449,13 +540,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -469,6 +557,34 @@
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -852,28 +968,28 @@
       <c r="A2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>10</v>
+      <c r="B2" s="27">
+        <v>45804</v>
       </c>
       <c r="C2" s="27">
         <v>45810</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="22">
         <v>3449993460</v>
       </c>
       <c r="F2" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="34"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="26" t="s">
@@ -885,22 +1001,22 @@
       <c r="C3" s="27">
         <v>45810</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="24">
         <v>132676879</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="29">
         <v>3449991556</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="H3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="35">
+      <c r="I3" s="34">
         <v>45800</v>
       </c>
     </row>
@@ -914,22 +1030,22 @@
       <c r="C4" s="27">
         <v>45810</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="24">
         <v>132691342</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="29">
         <v>3449992128</v>
       </c>
-      <c r="F4" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="32" t="s">
+      <c r="F4" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="35">
+      <c r="I4" s="34">
         <v>45802</v>
       </c>
     </row>
@@ -943,22 +1059,22 @@
       <c r="C5" s="27">
         <v>45810</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="24">
         <v>132712838</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>3449992920</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="H5" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="35">
+      <c r="I5" s="34">
         <v>45804</v>
       </c>
     </row>
@@ -972,22 +1088,22 @@
       <c r="C6" s="27">
         <v>45810</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="24">
         <v>132721217</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>3449993316</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="35">
+      <c r="I6" s="34">
         <v>45804</v>
       </c>
     </row>
@@ -1001,22 +1117,22 @@
       <c r="C7" s="27">
         <v>45810</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="24">
         <v>132720252</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>3449993240</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="H7" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="35">
+      <c r="I7" s="34">
         <v>45804</v>
       </c>
     </row>
@@ -1030,22 +1146,22 @@
       <c r="C8" s="27">
         <v>45810</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="24">
         <v>132750469</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>3449994812</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="H8" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="35">
+      <c r="I8" s="34">
         <v>45807</v>
       </c>
     </row>
@@ -1059,22 +1175,22 @@
       <c r="C9" s="27">
         <v>45810</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="24">
         <v>132741777</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>3449994493</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="35">
+      <c r="I9" s="34">
         <v>45805</v>
       </c>
     </row>
@@ -1088,22 +1204,22 @@
       <c r="C10" s="27">
         <v>45810</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="24">
         <v>132781244</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <v>3449996100</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="35">
+      <c r="I10" s="34">
         <v>45810</v>
       </c>
     </row>
@@ -1117,22 +1233,22 @@
       <c r="C11" s="27">
         <v>45810</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="24">
         <v>132776602</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>3449995912</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="32" t="s">
+      <c r="F11" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="35">
+      <c r="I11" s="34">
         <v>45806</v>
       </c>
     </row>
@@ -1146,22 +1262,22 @@
       <c r="C12" s="27">
         <v>45810</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="24">
         <v>132718170</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>3449993184</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="35">
+      <c r="I12" s="34">
         <v>45804</v>
       </c>
     </row>
@@ -1175,22 +1291,22 @@
       <c r="C13" s="27">
         <v>45810</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="24">
         <v>132675971</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>3449990302</v>
       </c>
-      <c r="F13" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="32" t="s">
+      <c r="F13" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="35">
+      <c r="I13" s="34">
         <v>45799</v>
       </c>
     </row>
@@ -1204,22 +1320,22 @@
       <c r="C14" s="27">
         <v>45810</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="24">
         <v>132697036</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>3449992315</v>
       </c>
-      <c r="F14" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="32" t="s">
+      <c r="F14" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="35">
+      <c r="I14" s="34">
         <v>45803</v>
       </c>
     </row>
@@ -1233,22 +1349,22 @@
       <c r="C15" s="27">
         <v>45810</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="24">
         <v>132676997</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>3449990566</v>
       </c>
-      <c r="F15" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="32" t="s">
+      <c r="F15" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="35">
+      <c r="I15" s="34">
         <v>45799</v>
       </c>
     </row>
@@ -1262,22 +1378,22 @@
       <c r="C16" s="27">
         <v>45810</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="24">
         <v>132683133</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>3449991787</v>
       </c>
-      <c r="F16" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="32" t="s">
+      <c r="F16" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="35">
+      <c r="I16" s="34">
         <v>45800</v>
       </c>
     </row>
@@ -1291,22 +1407,22 @@
       <c r="C17" s="27">
         <v>45810</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="24">
         <v>132684582</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>3449991864</v>
       </c>
-      <c r="F17" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="32" t="s">
+      <c r="F17" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="35">
+      <c r="I17" s="34">
         <v>45800</v>
       </c>
     </row>
@@ -1320,22 +1436,22 @@
       <c r="C18" s="27">
         <v>45810</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="24">
         <v>132701121</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>3449992502</v>
       </c>
-      <c r="F18" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="32" t="s">
+      <c r="F18" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="35">
+      <c r="I18" s="34">
         <v>45803</v>
       </c>
     </row>
@@ -1349,22 +1465,22 @@
       <c r="C19" s="27">
         <v>45810</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="24">
         <v>132686435</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>3449991974</v>
       </c>
-      <c r="F19" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="32" t="s">
+      <c r="F19" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="35">
+      <c r="I19" s="34">
         <v>45800</v>
       </c>
     </row>
@@ -1761,14 +1877,14 @@
   <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1796,7 +1912,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="44" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1804,173 +1920,359 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="7">
+        <v>45799</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="38">
+        <v>3449990863</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D3" s="14">
+        <v>3449992667</v>
+      </c>
+      <c r="E3" s="40">
+        <v>132704275</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="43">
+        <v>45803</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="7">
+        <v>45804</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D4" s="14">
+        <v>3449993393</v>
+      </c>
+      <c r="E4" s="40">
+        <v>132722398</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="43">
+        <v>45804</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="7">
+        <v>45804</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D5" s="14">
+        <v>3449993085</v>
+      </c>
+      <c r="E5" s="40">
+        <v>132716219</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="43">
+        <v>45804</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45805</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D6" s="14">
+        <v>3449994383</v>
+      </c>
+      <c r="E6" s="40">
+        <v>132739880</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="43">
+        <v>45810</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45809</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D7" s="14">
+        <v>3449994449</v>
+      </c>
+      <c r="E7" s="40">
+        <v>132740750</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="43">
+        <v>45810</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45807</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D8" s="14">
+        <v>3449996121</v>
+      </c>
+      <c r="E8" s="40">
+        <v>132781370</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="43">
+        <v>45811</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45807</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D9" s="14">
+        <v>3449995703</v>
+      </c>
+      <c r="E9" s="40">
+        <v>132771904</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="43">
+        <v>45807</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D10" s="14">
+        <v>3449992513</v>
+      </c>
+      <c r="E10" s="40">
+        <v>132701145</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="43">
+        <v>45803</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="B11" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D11" s="14">
+        <v>3449992634</v>
+      </c>
+      <c r="E11" s="40">
+        <v>132703944</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="43">
+        <v>45803</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="B12" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D12" s="14">
+        <v>3449992689</v>
+      </c>
+      <c r="E12" s="40">
+        <v>132704613</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="43">
+        <v>45803</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="B13" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45811</v>
+      </c>
+      <c r="D13" s="14">
+        <v>3449992799</v>
+      </c>
+      <c r="E13" s="40">
+        <v>132707276</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="43">
+        <v>45803</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="42"/>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
@@ -1978,12 +2280,9 @@
       <c r="F15" s="12"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
@@ -1991,12 +2290,9 @@
       <c r="F16" s="12"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
@@ -2004,12 +2300,9 @@
       <c r="F17" s="12"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8"/>
@@ -2017,12 +2310,9 @@
       <c r="F18" s="12"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
@@ -2030,9 +2320,8 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
-    </row>
-    <row r="20" spans="1:9">
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="6"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
@@ -2042,7 +2331,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:8">
       <c r="A21" s="6"/>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -2052,7 +2341,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:8">
       <c r="A22" s="6"/>
       <c r="B22" s="8"/>
       <c r="C22" s="7"/>
@@ -2062,7 +2351,7 @@
       <c r="G22" s="6"/>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:8">
       <c r="A23" s="6"/>
       <c r="B23" s="8"/>
       <c r="C23" s="7"/>
@@ -2072,7 +2361,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:8">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
       <c r="C24" s="7"/>
@@ -2082,7 +2371,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:8">
       <c r="A25" s="6"/>
       <c r="B25" s="8"/>
       <c r="C25" s="7"/>
@@ -2092,7 +2381,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:8">
       <c r="A26" s="6"/>
       <c r="B26" s="8"/>
       <c r="C26" s="7"/>
@@ -2102,7 +2391,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:8">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="7"/>
@@ -2112,7 +2401,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:8">
       <c r="A28" s="6"/>
       <c r="B28" s="8"/>
       <c r="C28" s="7"/>
@@ -2122,7 +2411,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:8">
       <c r="A29" s="6"/>
       <c r="B29" s="8"/>
       <c r="C29" s="7"/>
@@ -2132,7 +2421,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:8">
       <c r="A30" s="6"/>
       <c r="B30" s="8"/>
       <c r="C30" s="7"/>
@@ -2142,7 +2431,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:8">
       <c r="A31" s="6"/>
       <c r="B31" s="8"/>
       <c r="C31" s="7"/>
@@ -2152,7 +2441,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:8">
       <c r="A32" s="6"/>
       <c r="B32" s="8"/>
       <c r="C32" s="7"/>
@@ -2404,7 +2693,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5823,6 +6112,56 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -5830,7 +6169,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-470930</_dlc_DocId>
@@ -5873,9 +6212,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -5923,12 +6262,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -5937,12 +6276,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6025,7 +6364,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6044,7 +6383,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6077,7 +6416,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6155,8 +6494,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6245,68 +6584,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75FBB85C-E500-466F-A910-4F2EB96A6878}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B04BC8B6-8924-444F-8B5F-800A779B1CEF}"/>
 </file>